--- a/daily/2026-03-30.xlsx
+++ b/daily/2026-03-30.xlsx
@@ -13728,7 +13728,7 @@
       <c r="I2" s="3" t="n"/>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -14808,7 +14808,7 @@
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15072,7 @@
       <c r="I32" s="3" t="n"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       <c r="I46" s="3" t="n"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -16106,7 +16106,7 @@
       <c r="I55" s="3" t="n"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       <c r="I58" s="3" t="n"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -16312,7 +16312,7 @@
       <c r="I60" s="3" t="n"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17588,7 @@
       <c r="I88" s="3" t="n"/>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17852,7 @@
       <c r="I94" s="3" t="n"/>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18070,7 @@
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:07</t>
+          <t>2026-03-31 12:24</t>
         </is>
       </c>
     </row>
